--- a/Convert_from_xlsx_to_Json/table_normalization/environment-table16.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/environment-table16.xlsx
@@ -721,21 +721,14 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -749,6 +742,13 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1559,40 +1559,40 @@
       <c r="A4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="60"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="61" t="s">
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="60" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="20.149999999999999" customHeight="1">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="70" t="s">
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="67" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="87" customHeight="1">
-      <c r="A6" s="63"/>
+      <c r="A6" s="71"/>
       <c r="B6" s="8" t="s">
         <v>6</v>
       </c>
@@ -1620,7 +1620,7 @@
       <c r="J6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="71"/>
+      <c r="K6" s="68"/>
       <c r="L6" s="50"/>
       <c r="M6" s="50"/>
       <c r="N6" s="50"/>
@@ -3175,7 +3175,7 @@
       </c>
     </row>
     <row r="54" spans="1:11" ht="20.149999999999999" customHeight="1">
-      <c r="A54" s="67" t="s">
+      <c r="A54" s="64" t="s">
         <v>5</v>
       </c>
       <c r="B54" s="39">
@@ -3220,7 +3220,7 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="20.149999999999999" customHeight="1">
-      <c r="A55" s="68" t="s">
+      <c r="A55" s="65" t="s">
         <v>62</v>
       </c>
       <c r="B55" s="40">
@@ -3265,7 +3265,7 @@
       </c>
     </row>
     <row r="56" spans="1:11" ht="20.149999999999999" customHeight="1">
-      <c r="A56" s="68" t="s">
+      <c r="A56" s="65" t="s">
         <v>63</v>
       </c>
       <c r="B56" s="41">
@@ -3309,7 +3309,7 @@
       </c>
     </row>
     <row r="57" spans="1:11" ht="20.149999999999999" customHeight="1">
-      <c r="A57" s="68" t="s">
+      <c r="A57" s="65" t="s">
         <v>65</v>
       </c>
       <c r="B57" s="42">
@@ -3354,7 +3354,7 @@
       </c>
     </row>
     <row r="58" spans="1:11" ht="20.149999999999999" customHeight="1">
-      <c r="A58" s="69" t="s">
+      <c r="A58" s="66" t="s">
         <v>66</v>
       </c>
       <c r="B58" s="44">
@@ -3402,7 +3402,7 @@
       <c r="K59" s="47"/>
     </row>
     <row r="60" spans="1:11" s="4" customFormat="1" ht="36.75" customHeight="1">
-      <c r="A60" s="64" t="s">
+      <c r="A60" s="62" t="s">
         <v>67</v>
       </c>
       <c r="B60" s="47"/>
